--- a/Fixtures/formats/dates-1900.xlsx
+++ b/Fixtures/formats/dates-1900.xlsx
@@ -54,7 +54,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -69,40 +69,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1900-03-01</t>
+          <t>1900-02-28</t>
         </is>
       </c>
       <c r="B2" s="1">
-        <v>61.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>1900-03-01</t>
         </is>
       </c>
       <c r="B3" s="1">
-        <v>25569.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="B4" s="1">
-        <v>45366.0</v>
+        <v>25569.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="B5" s="1">
+        <v>45366.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>2099-12-31</t>
         </is>
       </c>
-      <c r="B5" s="1">
+      <c r="B6" s="1">
         <v>73050.0</v>
       </c>
     </row>
